--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/opinions.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/opinions.xlsx
@@ -9,6 +9,137 @@
     <sheet name="opinions_by_justice" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+  <si>
+    <t xml:space="preserve">Justice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opinion_Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Majority</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plaquemines Parish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hencely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Havana Docks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concurrence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elingburg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEO Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hain Celestial Grp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Callais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villarreal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dissent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coney Island Auto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bowe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enbridge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galette</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zorn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kagan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olivier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chiles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First Choice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kavanaugh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montgomery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urias-Orellana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAM Pension Fund</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R.W.</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -334,7 +465,701 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>23</v>
+      </c>
+      <c r="B31" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B32" t="s">
+        <v>19</v>
+      </c>
+      <c r="C32" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C33" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>29</v>
+      </c>
+      <c r="B34" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>29</v>
+      </c>
+      <c r="B35" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>29</v>
+      </c>
+      <c r="B36" t="s">
+        <v>13</v>
+      </c>
+      <c r="C36" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>29</v>
+      </c>
+      <c r="B37" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>29</v>
+      </c>
+      <c r="B38" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>32</v>
+      </c>
+      <c r="B39" t="s">
+        <v>4</v>
+      </c>
+      <c r="C39" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>32</v>
+      </c>
+      <c r="B40" t="s">
+        <v>4</v>
+      </c>
+      <c r="C40" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>32</v>
+      </c>
+      <c r="B41" t="s">
+        <v>4</v>
+      </c>
+      <c r="C41" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>32</v>
+      </c>
+      <c r="B42" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>32</v>
+      </c>
+      <c r="B43" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>32</v>
+      </c>
+      <c r="B44" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>32</v>
+      </c>
+      <c r="B45" t="s">
+        <v>19</v>
+      </c>
+      <c r="C45" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>35</v>
+      </c>
+      <c r="B46" t="s">
+        <v>4</v>
+      </c>
+      <c r="C46" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>35</v>
+      </c>
+      <c r="B47" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>35</v>
+      </c>
+      <c r="B48" t="s">
+        <v>19</v>
+      </c>
+      <c r="C48" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>34</v>
+      </c>
+      <c r="B49" t="s">
+        <v>4</v>
+      </c>
+      <c r="C49" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>34</v>
+      </c>
+      <c r="B50" t="s">
+        <v>4</v>
+      </c>
+      <c r="C50" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>34</v>
+      </c>
+      <c r="B51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>34</v>
+      </c>
+      <c r="B52" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" t="s">
+        <v>4</v>
+      </c>
+      <c r="C53" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" t="s">
+        <v>4</v>
+      </c>
+      <c r="C54" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>38</v>
+      </c>
+      <c r="B55" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>38</v>
+      </c>
+      <c r="B56" t="s">
+        <v>4</v>
+      </c>
+      <c r="C56" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>38</v>
+      </c>
+      <c r="B57" t="s">
+        <v>13</v>
+      </c>
+      <c r="C57" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>38</v>
+      </c>
+      <c r="B58" t="s">
+        <v>13</v>
+      </c>
+      <c r="C58" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>38</v>
+      </c>
+      <c r="B59" t="s">
+        <v>13</v>
+      </c>
+      <c r="C59" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>38</v>
+      </c>
+      <c r="B60" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>38</v>
+      </c>
+      <c r="B61" t="s">
+        <v>19</v>
+      </c>
+      <c r="C61" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>38</v>
+      </c>
+      <c r="B62" t="s">
+        <v>19</v>
+      </c>
+      <c r="C62" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>38</v>
+      </c>
+      <c r="B63" t="s">
+        <v>19</v>
+      </c>
+      <c r="C63" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>

--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/opinions.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/opinions.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t xml:space="preserve">Justice</t>
   </si>
@@ -35,6 +35,9 @@
     <t xml:space="preserve">Learning Resources</t>
   </si>
   <si>
+    <t xml:space="preserve">AT\&amp;T</t>
+  </si>
+  <si>
     <t xml:space="preserve">Thomas</t>
   </si>
   <si>
@@ -56,7 +59,7 @@
     <t xml:space="preserve">Concurrence</t>
   </si>
   <si>
-    <t xml:space="preserve">Elingburg</t>
+    <t xml:space="preserve">Ellingburg</t>
   </si>
   <si>
     <t xml:space="preserve">GEO Group</t>
@@ -71,9 +74,24 @@
     <t xml:space="preserve">Villarreal</t>
   </si>
   <si>
+    <t xml:space="preserve">Margolin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sripetch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keathley</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dissent</t>
   </si>
   <si>
+    <t xml:space="preserve">Hamm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whitton</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alito</t>
   </si>
   <si>
@@ -98,15 +116,24 @@
     <t xml:space="preserve">Jules</t>
   </si>
   <si>
+    <t xml:space="preserve">Fernandez</t>
+  </si>
+  <si>
     <t xml:space="preserve">Zorn</t>
   </si>
   <si>
+    <t xml:space="preserve">Rutherford</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kagan</t>
   </si>
   <si>
     <t xml:space="preserve">Olivier</t>
   </si>
   <si>
+    <t xml:space="preserve">Abouammo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Chiles</t>
   </si>
   <si>
@@ -116,9 +143,15 @@
     <t xml:space="preserve">First Choice</t>
   </si>
   <si>
+    <t xml:space="preserve">Flowers Foods</t>
+  </si>
+  <si>
     <t xml:space="preserve">Barrett</t>
   </si>
   <si>
+    <t xml:space="preserve">Pitchford</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kavanaugh</t>
   </si>
   <si>
@@ -135,6 +168,9 @@
   </si>
   <si>
     <t xml:space="preserve">IAM Pension Fund</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hikma</t>
   </si>
   <si>
     <t xml:space="preserve">R.W.</t>
@@ -501,18 +537,18 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
         <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>4</v>
@@ -523,7 +559,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
@@ -534,7 +570,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>4</v>
@@ -545,7 +581,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>4</v>
@@ -556,21 +592,21 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" t="s">
         <v>13</v>
-      </c>
-      <c r="C9" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
         <v>15</v>
@@ -578,10 +614,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
         <v>16</v>
@@ -589,10 +625,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
@@ -600,10 +636,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
@@ -611,120 +647,120 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" t="s">
         <v>19</v>
-      </c>
-      <c r="C14" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
         <v>20</v>
-      </c>
-      <c r="B15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C15" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B22" t="s">
         <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B23" t="s">
         <v>4</v>
       </c>
       <c r="C23" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B24" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C24" t="s">
         <v>16</v>
@@ -732,90 +768,90 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C26" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C27" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C28" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C29" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C30" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C31" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C32" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33">
@@ -826,7 +862,7 @@
         <v>4</v>
       </c>
       <c r="C33" t="s">
-        <v>2</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34">
@@ -834,10 +870,10 @@
         <v>29</v>
       </c>
       <c r="B34" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C34" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -845,10 +881,10 @@
         <v>29</v>
       </c>
       <c r="B35" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C35" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36">
@@ -856,10 +892,10 @@
         <v>29</v>
       </c>
       <c r="B36" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C36" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
@@ -867,10 +903,10 @@
         <v>29</v>
       </c>
       <c r="B37" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" t="s">
         <v>13</v>
-      </c>
-      <c r="C37" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="38">
@@ -878,249 +914,247 @@
         <v>29</v>
       </c>
       <c r="B38" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C38" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B39" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C39" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B40" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C40" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B41" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="C41" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B42" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C42" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C43" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C44" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B45" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C45" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B46" t="s">
         <v>4</v>
       </c>
       <c r="C46" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B47" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C47" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B48" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C48" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B49" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C49" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B50" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C50" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B51" t="s">
+        <v>23</v>
+      </c>
+      <c r="C51" t="s">
         <v>13</v>
-      </c>
-      <c r="C51" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B52" t="s">
-        <v>13</v>
-      </c>
-      <c r="C52" t="s">
-        <v>6</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="C52"/>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B53" t="s">
         <v>4</v>
       </c>
       <c r="C53" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B54" t="s">
         <v>4</v>
       </c>
       <c r="C54" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B55" t="s">
         <v>4</v>
       </c>
       <c r="C55" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B56" t="s">
         <v>4</v>
       </c>
       <c r="C56" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B57" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C57" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B58" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C58" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B59" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C59" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B60" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C60" t="s">
         <v>6</v>
@@ -1128,36 +1162,296 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B61" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C61" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B62" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C62" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B63" t="s">
+        <v>4</v>
+      </c>
+      <c r="C63" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>46</v>
+      </c>
+      <c r="B64" t="s">
+        <v>4</v>
+      </c>
+      <c r="C64" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>46</v>
+      </c>
+      <c r="B65" t="s">
+        <v>14</v>
+      </c>
+      <c r="C65" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>46</v>
+      </c>
+      <c r="B66" t="s">
+        <v>23</v>
+      </c>
+      <c r="C66" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>44</v>
+      </c>
+      <c r="B67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C67" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>44</v>
+      </c>
+      <c r="B68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C68" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>44</v>
+      </c>
+      <c r="B69" t="s">
+        <v>4</v>
+      </c>
+      <c r="C69" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>44</v>
+      </c>
+      <c r="B70" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>44</v>
+      </c>
+      <c r="B71" t="s">
+        <v>14</v>
+      </c>
+      <c r="C71" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>44</v>
+      </c>
+      <c r="B72" t="s">
+        <v>14</v>
+      </c>
+      <c r="C72" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>49</v>
+      </c>
+      <c r="B73" t="s">
+        <v>4</v>
+      </c>
+      <c r="C73" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>49</v>
+      </c>
+      <c r="B74" t="s">
+        <v>4</v>
+      </c>
+      <c r="C74" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>49</v>
+      </c>
+      <c r="B75" t="s">
+        <v>4</v>
+      </c>
+      <c r="C75" t="s">
         <v>19</v>
       </c>
-      <c r="C63" t="s">
-        <v>41</v>
-      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>49</v>
+      </c>
+      <c r="B76" t="s">
+        <v>4</v>
+      </c>
+      <c r="C76" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>49</v>
+      </c>
+      <c r="B77" t="s">
+        <v>4</v>
+      </c>
+      <c r="C77" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>49</v>
+      </c>
+      <c r="B78" t="s">
+        <v>4</v>
+      </c>
+      <c r="C78" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>49</v>
+      </c>
+      <c r="B79" t="s">
+        <v>14</v>
+      </c>
+      <c r="C79" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>49</v>
+      </c>
+      <c r="B80" t="s">
+        <v>14</v>
+      </c>
+      <c r="C80" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>49</v>
+      </c>
+      <c r="B81" t="s">
+        <v>14</v>
+      </c>
+      <c r="C81" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>49</v>
+      </c>
+      <c r="B82" t="s">
+        <v>14</v>
+      </c>
+      <c r="C82" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>49</v>
+      </c>
+      <c r="B83" t="s">
+        <v>23</v>
+      </c>
+      <c r="C83" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>49</v>
+      </c>
+      <c r="B84" t="s">
+        <v>23</v>
+      </c>
+      <c r="C84" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>49</v>
+      </c>
+      <c r="B85" t="s">
+        <v>23</v>
+      </c>
+      <c r="C85" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>49</v>
+      </c>
+      <c r="B86" t="s">
+        <v>23</v>
+      </c>
+      <c r="C86" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>49</v>
+      </c>
+      <c r="B87" t="s">
+        <v>23</v>
+      </c>
+      <c r="C87"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/opinions.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/opinions.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t xml:space="preserve">Justice</t>
   </si>
@@ -135,6 +135,9 @@
   </si>
   <si>
     <t xml:space="preserve">Chiles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FS Credit</t>
   </si>
   <si>
     <t xml:space="preserve">Gorsuch</t>
@@ -1070,11 +1073,13 @@
       <c r="B52" t="s">
         <v>23</v>
       </c>
-      <c r="C52"/>
+      <c r="C52" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B53" t="s">
         <v>4</v>
@@ -1085,18 +1090,18 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B54" t="s">
         <v>4</v>
       </c>
       <c r="C54" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B55" t="s">
         <v>4</v>
@@ -1107,18 +1112,18 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B56" t="s">
         <v>4</v>
       </c>
       <c r="C56" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B57" t="s">
         <v>4</v>
@@ -1129,18 +1134,18 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B58" t="s">
         <v>14</v>
       </c>
       <c r="C58" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B59" t="s">
         <v>14</v>
@@ -1151,7 +1156,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B60" t="s">
         <v>14</v>
@@ -1162,7 +1167,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B61" t="s">
         <v>23</v>
@@ -1173,18 +1178,18 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B62" t="s">
         <v>23</v>
       </c>
       <c r="C62" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B63" t="s">
         <v>4</v>
@@ -1195,29 +1200,29 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
+        <v>47</v>
+      </c>
+      <c r="B64" t="s">
+        <v>4</v>
+      </c>
+      <c r="C64" t="s">
         <v>46</v>
-      </c>
-      <c r="B64" t="s">
-        <v>4</v>
-      </c>
-      <c r="C64" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B65" t="s">
         <v>14</v>
       </c>
       <c r="C65" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B66" t="s">
         <v>23</v>
@@ -1228,29 +1233,29 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B67" t="s">
         <v>4</v>
       </c>
       <c r="C67" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B68" t="s">
         <v>4</v>
       </c>
       <c r="C68" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B69" t="s">
         <v>4</v>
@@ -1261,16 +1266,18 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B70" t="s">
         <v>4</v>
       </c>
-      <c r="C70"/>
+      <c r="C70" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B71" t="s">
         <v>14</v>
@@ -1281,7 +1288,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B72" t="s">
         <v>14</v>
@@ -1292,29 +1299,29 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B73" t="s">
         <v>4</v>
       </c>
       <c r="C73" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B74" t="s">
         <v>4</v>
       </c>
       <c r="C74" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B75" t="s">
         <v>4</v>
@@ -1325,29 +1332,29 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B76" t="s">
         <v>4</v>
       </c>
       <c r="C76" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B77" t="s">
         <v>4</v>
       </c>
       <c r="C77" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B78" t="s">
         <v>4</v>
@@ -1358,18 +1365,18 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
+        <v>50</v>
+      </c>
+      <c r="B79" t="s">
+        <v>14</v>
+      </c>
+      <c r="C79" t="s">
         <v>49</v>
-      </c>
-      <c r="B79" t="s">
-        <v>14</v>
-      </c>
-      <c r="C79" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B80" t="s">
         <v>14</v>
@@ -1380,7 +1387,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B81" t="s">
         <v>14</v>
@@ -1391,7 +1398,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B82" t="s">
         <v>14</v>
@@ -1402,7 +1409,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B83" t="s">
         <v>23</v>
@@ -1413,7 +1420,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B84" t="s">
         <v>23</v>
@@ -1424,18 +1431,18 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B85" t="s">
         <v>23</v>
       </c>
       <c r="C85" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B86" t="s">
         <v>23</v>
@@ -1446,12 +1453,14 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B87" t="s">
         <v>23</v>
       </c>
-      <c r="C87"/>
+      <c r="C87" t="s">
+        <v>41</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/opinions.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/opinions.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
   <si>
     <t xml:space="preserve">Justice</t>
   </si>
@@ -56,6 +56,9 @@
     <t xml:space="preserve">Havana Docks</t>
   </si>
   <si>
+    <t xml:space="preserve">Lau</t>
+  </si>
+  <si>
     <t xml:space="preserve">Concurrence</t>
   </si>
   <si>
@@ -83,6 +86,24 @@
     <t xml:space="preserve">Keathley</t>
   </si>
   <si>
+    <t xml:space="preserve">Hemani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UMD Medical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monsanto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Al Otro Lado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mullin v. Doe</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dissent</t>
   </si>
   <si>
@@ -92,12 +113,18 @@
     <t xml:space="preserve">Whitton</t>
   </si>
   <si>
+    <t xml:space="preserve">Hunter</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alito</t>
   </si>
   <si>
     <t xml:space="preserve">Coney Island Auto</t>
   </si>
   <si>
+    <t xml:space="preserve">Wolford</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rico</t>
   </si>
   <si>
@@ -125,6 +152,9 @@
     <t xml:space="preserve">Rutherford</t>
   </si>
   <si>
+    <t xml:space="preserve">Cisco</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kagan</t>
   </si>
   <si>
@@ -140,6 +170,9 @@
     <t xml:space="preserve">FS Credit</t>
   </si>
   <si>
+    <t xml:space="preserve">Exxon</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gorsuch</t>
   </si>
   <si>
@@ -147,6 +180,9 @@
   </si>
   <si>
     <t xml:space="preserve">Flowers Foods</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Landor</t>
   </si>
   <si>
     <t xml:space="preserve">Barrett</t>
@@ -609,10 +645,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" t="s">
         <v>14</v>
-      </c>
-      <c r="C10" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -620,7 +656,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
         <v>16</v>
@@ -631,7 +667,7 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
@@ -642,7 +678,7 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
@@ -653,7 +689,7 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
         <v>19</v>
@@ -664,7 +700,7 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
@@ -675,7 +711,7 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" t="s">
         <v>21</v>
@@ -686,7 +722,7 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" t="s">
         <v>22</v>
@@ -697,10 +733,10 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" t="s">
         <v>23</v>
-      </c>
-      <c r="C18" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -708,7 +744,7 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C19" t="s">
         <v>24</v>
@@ -719,7 +755,7 @@
         <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C20" t="s">
         <v>25</v>
@@ -730,18 +766,18 @@
         <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C22" t="s">
         <v>27</v>
@@ -749,175 +785,175 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C23" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C24" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C27" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C28" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="B29" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C29" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B30" t="s">
         <v>4</v>
       </c>
       <c r="C30" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B31" t="s">
         <v>4</v>
       </c>
       <c r="C31" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B32" t="s">
         <v>4</v>
       </c>
       <c r="C32" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B33" t="s">
         <v>4</v>
       </c>
       <c r="C33" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C34" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35" t="s">
         <v>29</v>
-      </c>
-      <c r="B35" t="s">
-        <v>14</v>
-      </c>
-      <c r="C35" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C36" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C37" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C38" t="s">
         <v>24</v>
@@ -925,142 +961,142 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B39" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C39" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B40" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C40" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B41" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C41" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B42" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C42" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B43" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C43" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B44" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C44" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B45" t="s">
         <v>4</v>
       </c>
       <c r="C45" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B46" t="s">
         <v>4</v>
       </c>
       <c r="C46" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B47" t="s">
         <v>4</v>
       </c>
       <c r="C47" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B48" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C48" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B49" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C49" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B50" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C50" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B51" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C51" t="s">
         <v>13</v>
@@ -1068,76 +1104,76 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B52" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C52" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B53" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C53" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B54" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C54" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B55" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C55" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B56" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C56" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B57" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C57" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B58" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C58" t="s">
         <v>45</v>
@@ -1145,46 +1181,46 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B59" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C59" t="s">
-        <v>2</v>
+        <v>46</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B60" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C60" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B61" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C61" t="s">
-        <v>30</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B62" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C62" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
     </row>
     <row r="63">
@@ -1195,7 +1231,7 @@
         <v>4</v>
       </c>
       <c r="C63" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="64">
@@ -1206,7 +1242,7 @@
         <v>4</v>
       </c>
       <c r="C64" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="65">
@@ -1214,10 +1250,10 @@
         <v>47</v>
       </c>
       <c r="B65" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C65" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
     </row>
     <row r="66">
@@ -1225,136 +1261,136 @@
         <v>47</v>
       </c>
       <c r="B66" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C66" t="s">
-        <v>6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B67" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C67" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B68" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C68" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B69" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C69" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B70" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C70" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B71" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C71" t="s">
-        <v>5</v>
+        <v>52</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B72" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C72" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B73" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C73" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
+        <v>53</v>
+      </c>
+      <c r="B74" t="s">
+        <v>4</v>
+      </c>
+      <c r="C74" t="s">
         <v>50</v>
-      </c>
-      <c r="B74" t="s">
-        <v>4</v>
-      </c>
-      <c r="C74" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B75" t="s">
         <v>4</v>
       </c>
       <c r="C75" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B76" t="s">
         <v>4</v>
       </c>
       <c r="C76" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B77" t="s">
         <v>4</v>
       </c>
       <c r="C77" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B78" t="s">
         <v>4</v>
@@ -1365,101 +1401,530 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B79" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C79" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B80" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C80" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B81" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C81" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B82" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C82" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B83" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C83" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B84" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C84" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B85" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C85" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B86" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C86" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
+        <v>59</v>
+      </c>
+      <c r="B87" t="s">
+        <v>4</v>
+      </c>
+      <c r="C87" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>59</v>
+      </c>
+      <c r="B88" t="s">
+        <v>4</v>
+      </c>
+      <c r="C88" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>59</v>
+      </c>
+      <c r="B89" t="s">
+        <v>4</v>
+      </c>
+      <c r="C89" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>59</v>
+      </c>
+      <c r="B90" t="s">
+        <v>4</v>
+      </c>
+      <c r="C90" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>59</v>
+      </c>
+      <c r="B91" t="s">
+        <v>15</v>
+      </c>
+      <c r="C91" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>59</v>
+      </c>
+      <c r="B92" t="s">
+        <v>15</v>
+      </c>
+      <c r="C92" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>59</v>
+      </c>
+      <c r="B93" t="s">
+        <v>30</v>
+      </c>
+      <c r="C93" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>57</v>
+      </c>
+      <c r="B94" t="s">
+        <v>4</v>
+      </c>
+      <c r="C94" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>57</v>
+      </c>
+      <c r="B95" t="s">
+        <v>4</v>
+      </c>
+      <c r="C95" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>57</v>
+      </c>
+      <c r="B96" t="s">
+        <v>4</v>
+      </c>
+      <c r="C96" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>57</v>
+      </c>
+      <c r="B97" t="s">
+        <v>4</v>
+      </c>
+      <c r="C97" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>57</v>
+      </c>
+      <c r="B98" t="s">
+        <v>4</v>
+      </c>
+      <c r="C98" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>57</v>
+      </c>
+      <c r="B99" t="s">
+        <v>4</v>
+      </c>
+      <c r="C99" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>57</v>
+      </c>
+      <c r="B100" t="s">
+        <v>15</v>
+      </c>
+      <c r="C100" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>57</v>
+      </c>
+      <c r="B101" t="s">
+        <v>15</v>
+      </c>
+      <c r="C101" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>57</v>
+      </c>
+      <c r="B102" t="s">
+        <v>15</v>
+      </c>
+      <c r="C102" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>57</v>
+      </c>
+      <c r="B103" t="s">
+        <v>15</v>
+      </c>
+      <c r="C103" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>57</v>
+      </c>
+      <c r="B104" t="s">
+        <v>30</v>
+      </c>
+      <c r="C104" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>62</v>
+      </c>
+      <c r="B105" t="s">
+        <v>4</v>
+      </c>
+      <c r="C105" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>62</v>
+      </c>
+      <c r="B106" t="s">
+        <v>4</v>
+      </c>
+      <c r="C106" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>62</v>
+      </c>
+      <c r="B107" t="s">
+        <v>4</v>
+      </c>
+      <c r="C107" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>62</v>
+      </c>
+      <c r="B108" t="s">
+        <v>4</v>
+      </c>
+      <c r="C108" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>62</v>
+      </c>
+      <c r="B109" t="s">
+        <v>4</v>
+      </c>
+      <c r="C109" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>62</v>
+      </c>
+      <c r="B110" t="s">
+        <v>4</v>
+      </c>
+      <c r="C110" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>62</v>
+      </c>
+      <c r="B111" t="s">
+        <v>15</v>
+      </c>
+      <c r="C111" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>62</v>
+      </c>
+      <c r="B112" t="s">
+        <v>15</v>
+      </c>
+      <c r="C112" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>62</v>
+      </c>
+      <c r="B113" t="s">
+        <v>15</v>
+      </c>
+      <c r="C113" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>62</v>
+      </c>
+      <c r="B114" t="s">
+        <v>15</v>
+      </c>
+      <c r="C114" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>62</v>
+      </c>
+      <c r="B115" t="s">
+        <v>15</v>
+      </c>
+      <c r="C115" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>62</v>
+      </c>
+      <c r="B116" t="s">
+        <v>15</v>
+      </c>
+      <c r="C116" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>62</v>
+      </c>
+      <c r="B117" t="s">
+        <v>30</v>
+      </c>
+      <c r="C117" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>62</v>
+      </c>
+      <c r="B118" t="s">
+        <v>30</v>
+      </c>
+      <c r="C118" t="s">
         <v>50</v>
       </c>
-      <c r="B87" t="s">
-        <v>23</v>
-      </c>
-      <c r="C87" t="s">
-        <v>41</v>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>62</v>
+      </c>
+      <c r="B119" t="s">
+        <v>30</v>
+      </c>
+      <c r="C119" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>62</v>
+      </c>
+      <c r="B120" t="s">
+        <v>30</v>
+      </c>
+      <c r="C120" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>62</v>
+      </c>
+      <c r="B121" t="s">
+        <v>30</v>
+      </c>
+      <c r="C121" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>62</v>
+      </c>
+      <c r="B122" t="s">
+        <v>30</v>
+      </c>
+      <c r="C122" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>62</v>
+      </c>
+      <c r="B123" t="s">
+        <v>30</v>
+      </c>
+      <c r="C123" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>62</v>
+      </c>
+      <c r="B124" t="s">
+        <v>30</v>
+      </c>
+      <c r="C124" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>62</v>
+      </c>
+      <c r="B125" t="s">
+        <v>30</v>
+      </c>
+      <c r="C125" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>62</v>
+      </c>
+      <c r="B126" t="s">
+        <v>30</v>
+      </c>
+      <c r="C126" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/opinions.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/opinions.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
   <si>
     <t xml:space="preserve">Justice</t>
   </si>
@@ -38,6 +38,12 @@
     <t xml:space="preserve">AT\&amp;T</t>
   </si>
   <si>
+    <t xml:space="preserve">Cook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slaughter</t>
+  </si>
+  <si>
     <t xml:space="preserve">Thomas</t>
   </si>
   <si>
@@ -126,6 +132,12 @@
   </si>
   <si>
     <t xml:space="preserve">Rico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Watson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chatrie</t>
   </si>
   <si>
     <t xml:space="preserve">Sotomayor</t>
@@ -587,29 +599,29 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
         <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>4</v>
@@ -620,7 +632,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>4</v>
@@ -631,7 +643,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
         <v>4</v>
@@ -642,7 +654,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
         <v>4</v>
@@ -653,32 +665,32 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" t="s">
         <v>15</v>
-      </c>
-      <c r="C11" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
@@ -686,10 +698,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C14" t="s">
         <v>19</v>
@@ -697,10 +709,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
@@ -708,10 +720,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C16" t="s">
         <v>21</v>
@@ -719,10 +731,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C17" t="s">
         <v>22</v>
@@ -730,10 +742,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C18" t="s">
         <v>23</v>
@@ -741,10 +753,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C19" t="s">
         <v>24</v>
@@ -752,10 +764,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C20" t="s">
         <v>25</v>
@@ -763,10 +775,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C21" t="s">
         <v>26</v>
@@ -774,10 +786,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C22" t="s">
         <v>27</v>
@@ -785,10 +797,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C23" t="s">
         <v>28</v>
@@ -796,10 +808,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C24" t="s">
         <v>29</v>
@@ -807,21 +819,21 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B25" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" t="s">
         <v>30</v>
-      </c>
-      <c r="C25" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C26" t="s">
         <v>31</v>
@@ -829,329 +841,329 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C27" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B28" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C29" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="B30" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C30" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="B31" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C31" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="B32" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C32" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B33" t="s">
         <v>4</v>
       </c>
       <c r="C33" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B34" t="s">
         <v>4</v>
       </c>
       <c r="C34" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B35" t="s">
         <v>4</v>
       </c>
       <c r="C35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C36" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C37" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C38" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C40" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B41" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B42" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C42" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B43" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B44" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C44" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B45" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C45" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B46" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B47" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C47" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B48" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C48" t="s">
-        <v>2</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B49" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C49" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B50" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C50" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B51" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C51" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B52" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C52" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B53" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C53" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B54" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C54" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B55" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C55" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B56" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C56" t="s">
         <v>12</v>
@@ -1159,76 +1171,76 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B57" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C57" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B58" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C58" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B59" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C59" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B60" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C60" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B61" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C61" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B62" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C62" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B63" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C63" t="s">
         <v>48</v>
@@ -1236,10 +1248,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B64" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C64" t="s">
         <v>49</v>
@@ -1247,321 +1259,321 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B65" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C65" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B66" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C66" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B67" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C67" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B68" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C68" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B69" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C69" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B70" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C70" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B71" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C71" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B72" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C72" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B73" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C73" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B74" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C74" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B75" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C75" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B76" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C76" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B77" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C77" t="s">
-        <v>55</v>
+        <v>15</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B78" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C78" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B79" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C79" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B80" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C80" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B81" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C81" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B82" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C82" t="s">
-        <v>2</v>
+        <v>54</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B83" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C83" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B84" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C84" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B85" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C85" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B86" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C86" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B87" t="s">
         <v>4</v>
       </c>
       <c r="C87" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B88" t="s">
         <v>4</v>
       </c>
       <c r="C88" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B89" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C89" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B90" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C90" t="s">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B91" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C91" t="s">
-        <v>60</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B92" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C92" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B93" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C93" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
     </row>
     <row r="94">
@@ -1569,10 +1581,10 @@
         <v>57</v>
       </c>
       <c r="B94" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C94" t="s">
-        <v>61</v>
+        <v>9</v>
       </c>
     </row>
     <row r="95">
@@ -1580,10 +1592,10 @@
         <v>57</v>
       </c>
       <c r="B95" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C95" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
     </row>
     <row r="96">
@@ -1591,340 +1603,516 @@
         <v>57</v>
       </c>
       <c r="B96" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C96" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B97" t="s">
         <v>4</v>
       </c>
       <c r="C97" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B98" t="s">
         <v>4</v>
       </c>
       <c r="C98" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B99" t="s">
         <v>4</v>
       </c>
       <c r="C99" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B100" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C100" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B101" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C101" t="s">
-        <v>6</v>
+        <v>64</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B102" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C102" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B103" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C103" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B104" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C104" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B105" t="s">
         <v>4</v>
       </c>
       <c r="C105" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B106" t="s">
         <v>4</v>
       </c>
       <c r="C106" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B107" t="s">
         <v>4</v>
       </c>
       <c r="C107" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B108" t="s">
         <v>4</v>
       </c>
       <c r="C108" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B109" t="s">
         <v>4</v>
       </c>
       <c r="C109" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B110" t="s">
         <v>4</v>
       </c>
       <c r="C110" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B111" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C111" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B112" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C112" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B113" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C113" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B114" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C114" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B115" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C115" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B116" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C116" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B117" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C117" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B118" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C118" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B119" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C119" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B120" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C120" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B121" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C121" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B122" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C122" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B123" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C123" t="s">
-        <v>14</v>
+        <v>69</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B124" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C124" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B125" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C125" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B126" t="s">
+        <v>17</v>
+      </c>
+      <c r="C126" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>66</v>
+      </c>
+      <c r="B127" t="s">
+        <v>17</v>
+      </c>
+      <c r="C127" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>66</v>
+      </c>
+      <c r="B128" t="s">
+        <v>17</v>
+      </c>
+      <c r="C128" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>66</v>
+      </c>
+      <c r="B129" t="s">
+        <v>17</v>
+      </c>
+      <c r="C129" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>66</v>
+      </c>
+      <c r="B130" t="s">
+        <v>17</v>
+      </c>
+      <c r="C130" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>66</v>
+      </c>
+      <c r="B131" t="s">
+        <v>17</v>
+      </c>
+      <c r="C131" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>66</v>
+      </c>
+      <c r="B132" t="s">
+        <v>17</v>
+      </c>
+      <c r="C132" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>66</v>
+      </c>
+      <c r="B133" t="s">
+        <v>32</v>
+      </c>
+      <c r="C133" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>66</v>
+      </c>
+      <c r="B134" t="s">
+        <v>32</v>
+      </c>
+      <c r="C134" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>66</v>
+      </c>
+      <c r="B135" t="s">
+        <v>32</v>
+      </c>
+      <c r="C135" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>66</v>
+      </c>
+      <c r="B136" t="s">
+        <v>32</v>
+      </c>
+      <c r="C136" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>66</v>
+      </c>
+      <c r="B137" t="s">
+        <v>32</v>
+      </c>
+      <c r="C137" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>66</v>
+      </c>
+      <c r="B138" t="s">
+        <v>32</v>
+      </c>
+      <c r="C138" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>66</v>
+      </c>
+      <c r="B139" t="s">
+        <v>32</v>
+      </c>
+      <c r="C139" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>66</v>
+      </c>
+      <c r="B140" t="s">
+        <v>32</v>
+      </c>
+      <c r="C140" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>66</v>
+      </c>
+      <c r="B141" t="s">
+        <v>32</v>
+      </c>
+      <c r="C141" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>66</v>
+      </c>
+      <c r="B142" t="s">
+        <v>32</v>
+      </c>
+      <c r="C142" t="s">
         <v>30</v>
-      </c>
-      <c r="C126" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/opinions.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/opinions.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
   <si>
     <t xml:space="preserve">Justice</t>
   </si>
@@ -44,6 +44,9 @@
     <t xml:space="preserve">Slaughter</t>
   </si>
   <si>
+    <t xml:space="preserve">Barbara</t>
+  </si>
+  <si>
     <t xml:space="preserve">Thomas</t>
   </si>
   <si>
@@ -110,6 +113,9 @@
     <t xml:space="preserve">Mullin v. Doe</t>
   </si>
   <si>
+    <t xml:space="preserve">B.P.J.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dissent</t>
   </si>
   <si>
@@ -183,6 +189,9 @@
   </si>
   <si>
     <t xml:space="preserve">Exxon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NRSC</t>
   </si>
   <si>
     <t xml:space="preserve">Gorsuch</t>
@@ -621,18 +630,18 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
         <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>4</v>
@@ -643,7 +652,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
         <v>4</v>
@@ -654,7 +663,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
         <v>4</v>
@@ -665,7 +674,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
         <v>4</v>
@@ -676,7 +685,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
         <v>4</v>
@@ -687,21 +696,21 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" t="s">
         <v>17</v>
-      </c>
-      <c r="C13" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
         <v>19</v>
@@ -709,10 +718,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
@@ -720,10 +729,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s">
         <v>21</v>
@@ -731,10 +740,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s">
         <v>22</v>
@@ -742,10 +751,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
         <v>23</v>
@@ -753,10 +762,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C19" t="s">
         <v>24</v>
@@ -764,10 +773,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C20" t="s">
         <v>25</v>
@@ -775,10 +784,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C21" t="s">
         <v>26</v>
@@ -786,10 +795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C22" t="s">
         <v>27</v>
@@ -797,10 +806,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C23" t="s">
         <v>28</v>
@@ -808,10 +817,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C24" t="s">
         <v>29</v>
@@ -819,10 +828,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C25" t="s">
         <v>30</v>
@@ -830,10 +839,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C26" t="s">
         <v>31</v>
@@ -841,21 +850,21 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" t="s">
         <v>32</v>
-      </c>
-      <c r="C27" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C28" t="s">
         <v>33</v>
@@ -863,54 +872,54 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C29" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C31" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C32" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="C33" t="s">
         <v>37</v>
@@ -918,142 +927,142 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="C34" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="C35" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B36" t="s">
         <v>4</v>
       </c>
       <c r="C36" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B37" t="s">
         <v>4</v>
       </c>
       <c r="C37" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B38" t="s">
         <v>4</v>
       </c>
       <c r="C38" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C39" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C40" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C41" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B42" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C42" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B43" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C43" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B44" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C44" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B45" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C45" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B46" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C46" t="s">
         <v>41</v>
@@ -1061,263 +1070,263 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B47" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C47" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
+        <v>38</v>
+      </c>
+      <c r="B48" t="s">
+        <v>34</v>
+      </c>
+      <c r="C48" t="s">
         <v>42</v>
-      </c>
-      <c r="B48" t="s">
-        <v>4</v>
-      </c>
-      <c r="C48" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B49" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="C49" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B50" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="C50" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B51" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="C51" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B52" t="s">
         <v>4</v>
       </c>
       <c r="C52" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B53" t="s">
         <v>4</v>
       </c>
       <c r="C53" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B54" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C54" t="s">
-        <v>2</v>
+        <v>47</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B55" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C55" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B56" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C56" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B57" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C57" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B58" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C58" t="s">
-        <v>33</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B59" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C59" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B60" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C60" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B61" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C61" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B62" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C62" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B63" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C63" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B64" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C64" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B65" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C65" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B66" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C66" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B67" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C67" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B68" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="C68" t="s">
-        <v>2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
+        <v>44</v>
+      </c>
+      <c r="B69" t="s">
+        <v>34</v>
+      </c>
+      <c r="C69" t="s">
         <v>51</v>
-      </c>
-      <c r="B69" t="s">
-        <v>4</v>
-      </c>
-      <c r="C69" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B70" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="C70" t="s">
         <v>52</v>
@@ -1325,98 +1334,98 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B71" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="C71" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B72" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="C72" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B73" t="s">
         <v>4</v>
       </c>
       <c r="C73" t="s">
-        <v>41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B74" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C74" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B75" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C75" t="s">
-        <v>6</v>
+        <v>54</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B76" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="C76" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B77" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="C77" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B78" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="C78" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B79" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C79" t="s">
         <v>56</v>
@@ -1424,109 +1433,109 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B80" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C80" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B81" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C81" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B82" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="C82" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
+        <v>53</v>
+      </c>
+      <c r="B83" t="s">
+        <v>34</v>
+      </c>
+      <c r="C83" t="s">
         <v>57</v>
-      </c>
-      <c r="B83" t="s">
-        <v>4</v>
-      </c>
-      <c r="C83" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B84" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="C84" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B85" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="C85" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B86" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="C86" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B87" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="C87" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B88" t="s">
         <v>4</v>
       </c>
       <c r="C88" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B89" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C89" t="s">
         <v>61</v>
@@ -1534,585 +1543,728 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B90" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C90" t="s">
-        <v>2</v>
+        <v>41</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B91" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C91" t="s">
-        <v>6</v>
+        <v>62</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B92" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C92" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B93" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C93" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B94" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C94" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B95" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C95" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B96" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C96" t="s">
-        <v>62</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B97" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C97" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B98" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C98" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B99" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C99" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B100" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C100" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B101" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C101" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B102" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C102" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B103" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C103" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B104" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C104" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B105" t="s">
         <v>4</v>
       </c>
       <c r="C105" t="s">
-        <v>65</v>
+        <v>19</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B106" t="s">
         <v>4</v>
       </c>
       <c r="C106" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B107" t="s">
         <v>4</v>
       </c>
       <c r="C107" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B108" t="s">
         <v>4</v>
       </c>
       <c r="C108" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B109" t="s">
         <v>4</v>
       </c>
       <c r="C109" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B110" t="s">
         <v>4</v>
       </c>
       <c r="C110" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B111" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C111" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B112" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C112" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B113" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C113" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B114" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C114" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B115" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C115" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B116" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="C116" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B117" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="C117" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B118" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="C118" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B119" t="s">
         <v>4</v>
       </c>
       <c r="C119" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B120" t="s">
         <v>4</v>
       </c>
       <c r="C120" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B121" t="s">
         <v>4</v>
       </c>
       <c r="C121" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B122" t="s">
         <v>4</v>
       </c>
       <c r="C122" t="s">
-        <v>68</v>
+        <v>42</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B123" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C123" t="s">
-        <v>69</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B124" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C124" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B125" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C125" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B126" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C126" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B127" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C127" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B128" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C128" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B129" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C129" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B130" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C130" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B131" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C131" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B132" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C132" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B133" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="C133" t="s">
-        <v>5</v>
+        <v>71</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B134" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="C134" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B135" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="C135" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B136" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C136" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B137" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C137" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B138" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C138" t="s">
-        <v>60</v>
+        <v>12</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B139" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C139" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B140" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C140" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B141" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C141" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B142" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C142" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>69</v>
+      </c>
+      <c r="B143" t="s">
+        <v>18</v>
+      </c>
+      <c r="C143" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>69</v>
+      </c>
+      <c r="B144" t="s">
+        <v>18</v>
+      </c>
+      <c r="C144" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>69</v>
+      </c>
+      <c r="B145" t="s">
+        <v>18</v>
+      </c>
+      <c r="C145" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>69</v>
+      </c>
+      <c r="B146" t="s">
+        <v>34</v>
+      </c>
+      <c r="C146" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>69</v>
+      </c>
+      <c r="B147" t="s">
+        <v>34</v>
+      </c>
+      <c r="C147" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>69</v>
+      </c>
+      <c r="B148" t="s">
+        <v>34</v>
+      </c>
+      <c r="C148" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>69</v>
+      </c>
+      <c r="B149" t="s">
+        <v>34</v>
+      </c>
+      <c r="C149" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>69</v>
+      </c>
+      <c r="B150" t="s">
+        <v>34</v>
+      </c>
+      <c r="C150" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>69</v>
+      </c>
+      <c r="B151" t="s">
+        <v>34</v>
+      </c>
+      <c r="C151" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>69</v>
+      </c>
+      <c r="B152" t="s">
+        <v>34</v>
+      </c>
+      <c r="C152" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>69</v>
+      </c>
+      <c r="B153" t="s">
+        <v>34</v>
+      </c>
+      <c r="C153" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>69</v>
+      </c>
+      <c r="B154" t="s">
+        <v>34</v>
+      </c>
+      <c r="C154" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>69</v>
+      </c>
+      <c r="B155" t="s">
+        <v>34</v>
+      </c>
+      <c r="C155" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
